--- a/events/Milan_2014_WC/Milan_2014_WC_Results.xlsx
+++ b/events/Milan_2014_WC/Milan_2014_WC_Results.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X991"/>
+  <dimension ref="A1:X1027"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69514,7 +69514,7 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
@@ -69524,7 +69524,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D972" t="n">
@@ -69545,43 +69545,32 @@
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>14:50:00</t>
+          <t>14:20:00</t>
         </is>
       </c>
       <c r="I972" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="K972" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>129</t>
         </is>
       </c>
       <c r="L972" t="n">
-        <v>110</v>
-      </c>
-      <c r="M972" t="n">
-        <v>1</v>
-      </c>
-      <c r="N972" t="n">
-        <v>1</v>
-      </c>
-      <c r="P972" t="inlineStr">
-        <is>
-          <t>23:28.235</t>
-        </is>
-      </c>
-      <c r="R972" t="inlineStr">
-        <is>
-          <t>50186</t>
+        <v>2</v>
+      </c>
+      <c r="X972" t="inlineStr">
+        <is>
+          <t>DNF</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -69591,7 +69580,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D973" t="n">
@@ -69612,41 +69601,30 @@
       </c>
       <c r="H973" t="inlineStr">
         <is>
-          <t>14:50:00</t>
+          <t>14:20:00</t>
         </is>
       </c>
       <c r="I973" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="K973" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>129</t>
         </is>
       </c>
       <c r="L973" t="n">
-        <v>111</v>
-      </c>
-      <c r="M973" t="n">
-        <v>2</v>
-      </c>
-      <c r="N973" t="n">
-        <v>2</v>
-      </c>
-      <c r="P973" t="inlineStr">
-        <is>
-          <t>23:34.967</t>
-        </is>
-      </c>
-      <c r="Q973" t="inlineStr">
-        <is>
-          <t>+6.732</t>
-        </is>
+        <v>12</v>
       </c>
       <c r="R973" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>45118</t>
+        </is>
+      </c>
+      <c r="X973" t="inlineStr">
+        <is>
+          <t>DNF</t>
         </is>
       </c>
     </row>
@@ -69689,7 +69667,7 @@
       </c>
       <c r="I974" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="K974" t="inlineStr">
@@ -69698,27 +69676,22 @@
         </is>
       </c>
       <c r="L974" t="n">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="M974" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N974" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P974" t="inlineStr">
         <is>
-          <t>23:39.895</t>
-        </is>
-      </c>
-      <c r="Q974" t="inlineStr">
-        <is>
-          <t>+11.660</t>
+          <t>23:28.235</t>
         </is>
       </c>
       <c r="R974" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>50186</t>
         </is>
       </c>
     </row>
@@ -69761,7 +69734,7 @@
       </c>
       <c r="I975" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="K975" t="inlineStr">
@@ -69770,27 +69743,27 @@
         </is>
       </c>
       <c r="L975" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="M975" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N975" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P975" t="inlineStr">
         <is>
-          <t>24:09.655</t>
+          <t>23:34.967</t>
         </is>
       </c>
       <c r="Q975" t="inlineStr">
         <is>
-          <t>+41.420</t>
+          <t>+6.732</t>
         </is>
       </c>
       <c r="R975" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>36283</t>
         </is>
       </c>
     </row>
@@ -69833,7 +69806,7 @@
       </c>
       <c r="I976" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="K976" t="inlineStr">
@@ -69842,27 +69815,27 @@
         </is>
       </c>
       <c r="L976" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="M976" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N976" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P976" t="inlineStr">
         <is>
-          <t>24:12.751</t>
+          <t>23:39.895</t>
         </is>
       </c>
       <c r="Q976" t="inlineStr">
         <is>
-          <t>+44.516</t>
+          <t>+11.660</t>
         </is>
       </c>
       <c r="R976" t="inlineStr">
         <is>
-          <t>35779</t>
+          <t>52281</t>
         </is>
       </c>
     </row>
@@ -69905,7 +69878,7 @@
       </c>
       <c r="I977" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="K977" t="inlineStr">
@@ -69914,27 +69887,27 @@
         </is>
       </c>
       <c r="L977" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M977" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N977" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P977" t="inlineStr">
         <is>
-          <t>24:13.815</t>
+          <t>24:09.655</t>
         </is>
       </c>
       <c r="Q977" t="inlineStr">
         <is>
-          <t>+45.580</t>
+          <t>+41.420</t>
         </is>
       </c>
       <c r="R977" t="inlineStr">
         <is>
-          <t>42770</t>
+          <t>42453</t>
         </is>
       </c>
     </row>
@@ -69977,7 +69950,7 @@
       </c>
       <c r="I978" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="K978" t="inlineStr">
@@ -69986,27 +69959,27 @@
         </is>
       </c>
       <c r="L978" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M978" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N978" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P978" t="inlineStr">
         <is>
-          <t>24:14.543</t>
+          <t>24:12.751</t>
         </is>
       </c>
       <c r="Q978" t="inlineStr">
         <is>
-          <t>+46.308</t>
+          <t>+44.516</t>
         </is>
       </c>
       <c r="R978" t="inlineStr">
         <is>
-          <t>36579</t>
+          <t>35779</t>
         </is>
       </c>
     </row>
@@ -70049,7 +70022,7 @@
       </c>
       <c r="I979" t="inlineStr">
         <is>
-          <t>NED</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="K979" t="inlineStr">
@@ -70058,27 +70031,27 @@
         </is>
       </c>
       <c r="L979" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M979" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N979" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P979" t="inlineStr">
         <is>
-          <t>24:15.623</t>
+          <t>24:13.815</t>
         </is>
       </c>
       <c r="Q979" t="inlineStr">
         <is>
-          <t>+47.388</t>
+          <t>+45.580</t>
         </is>
       </c>
       <c r="R979" t="inlineStr">
         <is>
-          <t>35924</t>
+          <t>42770</t>
         </is>
       </c>
     </row>
@@ -70121,7 +70094,7 @@
       </c>
       <c r="I980" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="K980" t="inlineStr">
@@ -70130,27 +70103,27 @@
         </is>
       </c>
       <c r="L980" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="M980" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N980" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P980" t="inlineStr">
         <is>
-          <t>24:32.139</t>
+          <t>24:14.543</t>
         </is>
       </c>
       <c r="Q980" t="inlineStr">
         <is>
-          <t>+63.904</t>
+          <t>+46.308</t>
         </is>
       </c>
       <c r="R980" t="inlineStr">
         <is>
-          <t>42797</t>
+          <t>36579</t>
         </is>
       </c>
     </row>
@@ -70193,7 +70166,7 @@
       </c>
       <c r="I981" t="inlineStr">
         <is>
-          <t>BUL</t>
+          <t>NED</t>
         </is>
       </c>
       <c r="K981" t="inlineStr">
@@ -70202,29 +70175,34 @@
         </is>
       </c>
       <c r="L981" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="M981" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N981" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P981" t="inlineStr">
         <is>
-          <t>24:44.131</t>
+          <t>24:15.623</t>
         </is>
       </c>
       <c r="Q981" t="inlineStr">
         <is>
-          <t>+75.896</t>
+          <t>+47.388</t>
+        </is>
+      </c>
+      <c r="R981" t="inlineStr">
+        <is>
+          <t>35924</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
@@ -70255,43 +70233,48 @@
       </c>
       <c r="H982" t="inlineStr">
         <is>
-          <t>15:20:00</t>
+          <t>14:50:00</t>
         </is>
       </c>
       <c r="I982" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="K982" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L982" t="n">
-        <v>226</v>
+        <v>120</v>
       </c>
       <c r="M982" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N982" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P982" t="inlineStr">
         <is>
-          <t>20:53.033</t>
+          <t>24:32.139</t>
+        </is>
+      </c>
+      <c r="Q982" t="inlineStr">
+        <is>
+          <t>+63.904</t>
         </is>
       </c>
       <c r="R982" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>42797</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -70322,48 +70305,43 @@
       </c>
       <c r="H983" t="inlineStr">
         <is>
-          <t>15:20:00</t>
+          <t>14:50:00</t>
         </is>
       </c>
       <c r="I983" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BUL</t>
         </is>
       </c>
       <c r="K983" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L983" t="n">
-        <v>231</v>
+        <v>108</v>
       </c>
       <c r="M983" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N983" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P983" t="inlineStr">
         <is>
-          <t>20:54.245</t>
+          <t>24:44.131</t>
         </is>
       </c>
       <c r="Q983" t="inlineStr">
         <is>
-          <t>+1.212</t>
-        </is>
-      </c>
-      <c r="R983" t="inlineStr">
-        <is>
-          <t>36448</t>
+          <t>+75.896</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
@@ -70394,48 +70372,48 @@
       </c>
       <c r="H984" t="inlineStr">
         <is>
-          <t>15:20:00</t>
+          <t>14:50:00</t>
         </is>
       </c>
       <c r="I984" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="K984" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L984" t="n">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="M984" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N984" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P984" t="inlineStr">
         <is>
-          <t>20:54.525</t>
+          <t>24:45.059</t>
         </is>
       </c>
       <c r="Q984" t="inlineStr">
         <is>
-          <t>+1.492</t>
+          <t>+76.824</t>
         </is>
       </c>
       <c r="R984" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>42380</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
@@ -70466,48 +70444,43 @@
       </c>
       <c r="H985" t="inlineStr">
         <is>
-          <t>15:20:00</t>
+          <t>14:50:00</t>
         </is>
       </c>
       <c r="I985" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="K985" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L985" t="n">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="M985" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N985" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P985" t="inlineStr">
         <is>
-          <t>21:13.621</t>
-        </is>
-      </c>
-      <c r="Q985" t="inlineStr">
-        <is>
-          <t>+20.588</t>
+          <t>25:16.171</t>
         </is>
       </c>
       <c r="R985" t="inlineStr">
         <is>
-          <t>42769</t>
+          <t>35897</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
@@ -70538,48 +70511,43 @@
       </c>
       <c r="H986" t="inlineStr">
         <is>
-          <t>15:20:00</t>
+          <t>14:50:00</t>
         </is>
       </c>
       <c r="I986" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="K986" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L986" t="n">
-        <v>225</v>
+        <v>109</v>
       </c>
       <c r="M986" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N986" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="P986" t="inlineStr">
         <is>
-          <t>21:30.389</t>
-        </is>
-      </c>
-      <c r="Q986" t="inlineStr">
-        <is>
-          <t>+37.356</t>
+          <t>25:25.175</t>
         </is>
       </c>
       <c r="R986" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>52198</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
@@ -70610,48 +70578,43 @@
       </c>
       <c r="H987" t="inlineStr">
         <is>
-          <t>15:20:00</t>
+          <t>14:50:00</t>
         </is>
       </c>
       <c r="I987" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="K987" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L987" t="n">
-        <v>212</v>
+        <v>117</v>
       </c>
       <c r="M987" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N987" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P987" t="inlineStr">
         <is>
-          <t>21:30.629</t>
-        </is>
-      </c>
-      <c r="Q987" t="inlineStr">
-        <is>
-          <t>+37.596</t>
+          <t>25:32.235</t>
         </is>
       </c>
       <c r="R987" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>42381</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
@@ -70682,48 +70645,38 @@
       </c>
       <c r="H988" t="inlineStr">
         <is>
-          <t>15:20:00</t>
+          <t>14:50:00</t>
         </is>
       </c>
       <c r="I988" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>NED</t>
         </is>
       </c>
       <c r="K988" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L988" t="n">
-        <v>203</v>
+        <v>119</v>
       </c>
       <c r="M988" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N988" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P988" t="inlineStr">
         <is>
-          <t>21:35.437</t>
-        </is>
-      </c>
-      <c r="Q988" t="inlineStr">
-        <is>
-          <t>+42.404</t>
-        </is>
-      </c>
-      <c r="R988" t="inlineStr">
-        <is>
-          <t>49661</t>
+          <t>25:36.055</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -70754,48 +70707,38 @@
       </c>
       <c r="H989" t="inlineStr">
         <is>
-          <t>15:20:00</t>
+          <t>14:50:00</t>
         </is>
       </c>
       <c r="I989" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="K989" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L989" t="n">
-        <v>232</v>
+        <v>101</v>
       </c>
       <c r="M989" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N989" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P989" t="inlineStr">
         <is>
-          <t>21:40.285</t>
-        </is>
-      </c>
-      <c r="Q989" t="inlineStr">
-        <is>
-          <t>+47.252</t>
-        </is>
-      </c>
-      <c r="R989" t="inlineStr">
-        <is>
-          <t>42285</t>
+          <t>26:30.123</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
@@ -70826,48 +70769,37 @@
       </c>
       <c r="H990" t="inlineStr">
         <is>
-          <t>15:20:00</t>
+          <t>14:50:00</t>
         </is>
       </c>
       <c r="I990" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="K990" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L990" t="n">
-        <v>216</v>
-      </c>
-      <c r="M990" t="n">
-        <v>9</v>
-      </c>
-      <c r="N990" t="n">
-        <v>9</v>
-      </c>
-      <c r="P990" t="inlineStr">
-        <is>
-          <t>21:41.269</t>
-        </is>
-      </c>
-      <c r="Q990" t="inlineStr">
-        <is>
-          <t>+48.236</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="R990" t="inlineStr">
         <is>
-          <t>47415</t>
+          <t>52182</t>
+        </is>
+      </c>
+      <c r="X990" t="inlineStr">
+        <is>
+          <t>DNF</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
@@ -70898,41 +70830,2420 @@
       </c>
       <c r="H991" t="inlineStr">
         <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="K991" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="L991" t="n">
+        <v>10</v>
+      </c>
+      <c r="R991" t="inlineStr">
+        <is>
+          <t>36600</t>
+        </is>
+      </c>
+      <c r="X991" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D992" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G992" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>SLO</t>
+        </is>
+      </c>
+      <c r="K992" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="L992" t="n">
+        <v>11</v>
+      </c>
+      <c r="R992" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
+      <c r="X992" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D993" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G993" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="L993" t="n">
+        <v>12</v>
+      </c>
+      <c r="X993" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D994" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G994" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="L994" t="n">
+        <v>10</v>
+      </c>
+      <c r="X994" t="inlineStr">
+        <is>
+          <t>DNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D995" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G995" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>ECU</t>
+        </is>
+      </c>
+      <c r="K995" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="L995" t="n">
+        <v>11</v>
+      </c>
+      <c r="R995" t="inlineStr">
+        <is>
+          <t>51940</t>
+        </is>
+      </c>
+      <c r="X995" t="inlineStr">
+        <is>
+          <t>DNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D996" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G996" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
           <t>15:20:00</t>
         </is>
       </c>
-      <c r="I991" t="inlineStr">
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="K996" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L996" t="n">
+        <v>226</v>
+      </c>
+      <c r="M996" t="n">
+        <v>1</v>
+      </c>
+      <c r="N996" t="n">
+        <v>1</v>
+      </c>
+      <c r="P996" t="inlineStr">
+        <is>
+          <t>20:53.033</t>
+        </is>
+      </c>
+      <c r="R996" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D997" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G997" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="K997" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L997" t="n">
+        <v>231</v>
+      </c>
+      <c r="M997" t="n">
+        <v>2</v>
+      </c>
+      <c r="N997" t="n">
+        <v>2</v>
+      </c>
+      <c r="P997" t="inlineStr">
+        <is>
+          <t>20:54.245</t>
+        </is>
+      </c>
+      <c r="Q997" t="inlineStr">
+        <is>
+          <t>+1.212</t>
+        </is>
+      </c>
+      <c r="R997" t="inlineStr">
+        <is>
+          <t>36448</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D998" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G998" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>GER</t>
+        </is>
+      </c>
+      <c r="K998" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L998" t="n">
+        <v>205</v>
+      </c>
+      <c r="M998" t="n">
+        <v>3</v>
+      </c>
+      <c r="N998" t="n">
+        <v>3</v>
+      </c>
+      <c r="P998" t="inlineStr">
+        <is>
+          <t>20:54.525</t>
+        </is>
+      </c>
+      <c r="Q998" t="inlineStr">
+        <is>
+          <t>+1.492</t>
+        </is>
+      </c>
+      <c r="R998" t="inlineStr">
+        <is>
+          <t>35707</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D999" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G999" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="K999" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L999" t="n">
+        <v>204</v>
+      </c>
+      <c r="M999" t="n">
+        <v>4</v>
+      </c>
+      <c r="N999" t="n">
+        <v>4</v>
+      </c>
+      <c r="P999" t="inlineStr">
+        <is>
+          <t>21:13.621</t>
+        </is>
+      </c>
+      <c r="Q999" t="inlineStr">
+        <is>
+          <t>+20.588</t>
+        </is>
+      </c>
+      <c r="R999" t="inlineStr">
+        <is>
+          <t>42769</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1000" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1000" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="K1000" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1000" t="n">
+        <v>225</v>
+      </c>
+      <c r="M1000" t="n">
+        <v>5</v>
+      </c>
+      <c r="N1000" t="n">
+        <v>5</v>
+      </c>
+      <c r="P1000" t="inlineStr">
+        <is>
+          <t>21:30.389</t>
+        </is>
+      </c>
+      <c r="Q1000" t="inlineStr">
+        <is>
+          <t>+37.356</t>
+        </is>
+      </c>
+      <c r="R1000" t="inlineStr">
+        <is>
+          <t>42336</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1001" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1001" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>SLO</t>
+        </is>
+      </c>
+      <c r="K1001" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1001" t="n">
+        <v>212</v>
+      </c>
+      <c r="M1001" t="n">
+        <v>6</v>
+      </c>
+      <c r="N1001" t="n">
+        <v>6</v>
+      </c>
+      <c r="P1001" t="inlineStr">
+        <is>
+          <t>21:30.629</t>
+        </is>
+      </c>
+      <c r="Q1001" t="inlineStr">
+        <is>
+          <t>+37.596</t>
+        </is>
+      </c>
+      <c r="R1001" t="inlineStr">
+        <is>
+          <t>36310</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1002" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1002" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="K1002" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1002" t="n">
+        <v>203</v>
+      </c>
+      <c r="M1002" t="n">
+        <v>7</v>
+      </c>
+      <c r="N1002" t="n">
+        <v>7</v>
+      </c>
+      <c r="P1002" t="inlineStr">
+        <is>
+          <t>21:35.437</t>
+        </is>
+      </c>
+      <c r="Q1002" t="inlineStr">
+        <is>
+          <t>+42.404</t>
+        </is>
+      </c>
+      <c r="R1002" t="inlineStr">
+        <is>
+          <t>49661</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1003" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1003" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1003" t="n">
+        <v>232</v>
+      </c>
+      <c r="M1003" t="n">
+        <v>8</v>
+      </c>
+      <c r="N1003" t="n">
+        <v>8</v>
+      </c>
+      <c r="P1003" t="inlineStr">
+        <is>
+          <t>21:40.285</t>
+        </is>
+      </c>
+      <c r="Q1003" t="inlineStr">
+        <is>
+          <t>+47.252</t>
+        </is>
+      </c>
+      <c r="R1003" t="inlineStr">
+        <is>
+          <t>42285</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1004" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1004" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="K1004" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1004" t="n">
+        <v>216</v>
+      </c>
+      <c r="M1004" t="n">
+        <v>9</v>
+      </c>
+      <c r="N1004" t="n">
+        <v>9</v>
+      </c>
+      <c r="P1004" t="inlineStr">
+        <is>
+          <t>21:41.269</t>
+        </is>
+      </c>
+      <c r="Q1004" t="inlineStr">
+        <is>
+          <t>+48.236</t>
+        </is>
+      </c>
+      <c r="R1004" t="inlineStr">
+        <is>
+          <t>47415</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1005" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1005" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
         <is>
           <t>SRB</t>
         </is>
       </c>
-      <c r="K991" t="inlineStr">
+      <c r="K1005" t="inlineStr">
         <is>
           <t>131</t>
         </is>
       </c>
-      <c r="L991" t="n">
+      <c r="L1005" t="n">
         <v>210</v>
       </c>
-      <c r="M991" t="n">
+      <c r="M1005" t="n">
         <v>10</v>
       </c>
-      <c r="N991" t="n">
+      <c r="N1005" t="n">
         <v>10</v>
       </c>
-      <c r="P991" t="inlineStr">
+      <c r="P1005" t="inlineStr">
         <is>
           <t>21:55.241</t>
         </is>
       </c>
-      <c r="Q991" t="inlineStr">
+      <c r="Q1005" t="inlineStr">
         <is>
           <t>+62.208</t>
         </is>
       </c>
-      <c r="R991" t="inlineStr">
+      <c r="R1005" t="inlineStr">
         <is>
           <t>42184</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1006" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1006" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="K1006" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1006" t="n">
+        <v>224</v>
+      </c>
+      <c r="M1006" t="n">
+        <v>11</v>
+      </c>
+      <c r="N1006" t="n">
+        <v>11</v>
+      </c>
+      <c r="P1006" t="inlineStr">
+        <is>
+          <t>22:03.909</t>
+        </is>
+      </c>
+      <c r="Q1006" t="inlineStr">
+        <is>
+          <t>+70.876</t>
+        </is>
+      </c>
+      <c r="R1006" t="inlineStr">
+        <is>
+          <t>42422</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1007" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1007" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>SLO</t>
+        </is>
+      </c>
+      <c r="K1007" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1007" t="n">
+        <v>222</v>
+      </c>
+      <c r="M1007" t="n">
+        <v>12</v>
+      </c>
+      <c r="N1007" t="n">
+        <v>12</v>
+      </c>
+      <c r="P1007" t="inlineStr">
+        <is>
+          <t>22:19.537</t>
+        </is>
+      </c>
+      <c r="Q1007" t="inlineStr">
+        <is>
+          <t>+86.504</t>
+        </is>
+      </c>
+      <c r="R1007" t="inlineStr">
+        <is>
+          <t>38164</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1008" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1008" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="K1008" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1008" t="n">
+        <v>201</v>
+      </c>
+      <c r="M1008" t="n">
+        <v>13</v>
+      </c>
+      <c r="N1008" t="n">
+        <v>13</v>
+      </c>
+      <c r="P1008" t="inlineStr">
+        <is>
+          <t>22:20.641</t>
+        </is>
+      </c>
+      <c r="Q1008" t="inlineStr">
+        <is>
+          <t>+87.608</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1009" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1009" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="K1009" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1009" t="n">
+        <v>220</v>
+      </c>
+      <c r="M1009" t="n">
+        <v>14</v>
+      </c>
+      <c r="N1009" t="n">
+        <v>14</v>
+      </c>
+      <c r="P1009" t="inlineStr">
+        <is>
+          <t>22:32.821</t>
+        </is>
+      </c>
+      <c r="Q1009" t="inlineStr">
+        <is>
+          <t>+99.788</t>
+        </is>
+      </c>
+      <c r="R1009" t="inlineStr">
+        <is>
+          <t>52099</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1010" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1010" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="K1010" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1010" t="n">
+        <v>223</v>
+      </c>
+      <c r="M1010" t="n">
+        <v>15</v>
+      </c>
+      <c r="N1010" t="n">
+        <v>15</v>
+      </c>
+      <c r="P1010" t="inlineStr">
+        <is>
+          <t>22:34.297</t>
+        </is>
+      </c>
+      <c r="R1010" t="inlineStr">
+        <is>
+          <t>36446</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1011" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1011" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>UZB</t>
+        </is>
+      </c>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1011" t="n">
+        <v>206</v>
+      </c>
+      <c r="M1011" t="n">
+        <v>16</v>
+      </c>
+      <c r="N1011" t="n">
+        <v>16</v>
+      </c>
+      <c r="P1011" t="inlineStr">
+        <is>
+          <t>22:36.113</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1012" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1012" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="K1012" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1012" t="n">
+        <v>208</v>
+      </c>
+      <c r="M1012" t="n">
+        <v>17</v>
+      </c>
+      <c r="N1012" t="n">
+        <v>17</v>
+      </c>
+      <c r="P1012" t="inlineStr">
+        <is>
+          <t>22:51.289</t>
+        </is>
+      </c>
+      <c r="R1012" t="inlineStr">
+        <is>
+          <t>36450</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1013" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1013" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>SRB</t>
+        </is>
+      </c>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1013" t="n">
+        <v>217</v>
+      </c>
+      <c r="M1013" t="n">
+        <v>18</v>
+      </c>
+      <c r="N1013" t="n">
+        <v>18</v>
+      </c>
+      <c r="P1013" t="inlineStr">
+        <is>
+          <t>22:52.865</t>
+        </is>
+      </c>
+      <c r="R1013" t="inlineStr">
+        <is>
+          <t>42179</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1014" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1014" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>RSA</t>
+        </is>
+      </c>
+      <c r="K1014" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1014" t="n">
+        <v>209</v>
+      </c>
+      <c r="M1014" t="n">
+        <v>19</v>
+      </c>
+      <c r="N1014" t="n">
+        <v>19</v>
+      </c>
+      <c r="P1014" t="inlineStr">
+        <is>
+          <t>22:54.233</t>
+        </is>
+      </c>
+      <c r="R1014" t="inlineStr">
+        <is>
+          <t>48405</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1015" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1015" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="K1015" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1015" t="n">
+        <v>230</v>
+      </c>
+      <c r="M1015" t="n">
+        <v>20</v>
+      </c>
+      <c r="N1015" t="n">
+        <v>20</v>
+      </c>
+      <c r="P1015" t="inlineStr">
+        <is>
+          <t>22:55.261</t>
+        </is>
+      </c>
+      <c r="R1015" t="inlineStr">
+        <is>
+          <t>36604</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1016" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1016" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="K1016" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1016" t="n">
+        <v>202</v>
+      </c>
+      <c r="M1016" t="n">
+        <v>21</v>
+      </c>
+      <c r="N1016" t="n">
+        <v>21</v>
+      </c>
+      <c r="P1016" t="inlineStr">
+        <is>
+          <t>23:02.093</t>
+        </is>
+      </c>
+      <c r="R1016" t="inlineStr">
+        <is>
+          <t>44434</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1017" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1017" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="K1017" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1017" t="n">
+        <v>221</v>
+      </c>
+      <c r="M1017" t="n">
+        <v>22</v>
+      </c>
+      <c r="N1017" t="n">
+        <v>22</v>
+      </c>
+      <c r="P1017" t="inlineStr">
+        <is>
+          <t>23:16.461</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1018" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1018" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1018" t="n">
+        <v>207</v>
+      </c>
+      <c r="M1018" t="n">
+        <v>23</v>
+      </c>
+      <c r="N1018" t="n">
+        <v>23</v>
+      </c>
+      <c r="P1018" t="inlineStr">
+        <is>
+          <t>23:17.069</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1019" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1019" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>SUI</t>
+        </is>
+      </c>
+      <c r="K1019" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1019" t="n">
+        <v>227</v>
+      </c>
+      <c r="M1019" t="n">
+        <v>24</v>
+      </c>
+      <c r="N1019" t="n">
+        <v>24</v>
+      </c>
+      <c r="P1019" t="inlineStr">
+        <is>
+          <t>23:18.981</t>
+        </is>
+      </c>
+      <c r="R1019" t="inlineStr">
+        <is>
+          <t>42377</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1020" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1020" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>UZB</t>
+        </is>
+      </c>
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1020" t="n">
+        <v>213</v>
+      </c>
+      <c r="M1020" t="n">
+        <v>25</v>
+      </c>
+      <c r="N1020" t="n">
+        <v>25</v>
+      </c>
+      <c r="P1020" t="inlineStr">
+        <is>
+          <t>23:31.437</t>
+        </is>
+      </c>
+      <c r="R1020" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1021" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1021" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>IRL</t>
+        </is>
+      </c>
+      <c r="K1021" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1021" t="n">
+        <v>228</v>
+      </c>
+      <c r="M1021" t="n">
+        <v>26</v>
+      </c>
+      <c r="N1021" t="n">
+        <v>26</v>
+      </c>
+      <c r="P1021" t="inlineStr">
+        <is>
+          <t>23:34.941</t>
+        </is>
+      </c>
+      <c r="R1021" t="inlineStr">
+        <is>
+          <t>42798</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1022" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1022" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="K1022" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1022" t="n">
+        <v>229</v>
+      </c>
+      <c r="M1022" t="n">
+        <v>27</v>
+      </c>
+      <c r="N1022" t="n">
+        <v>27</v>
+      </c>
+      <c r="P1022" t="inlineStr">
+        <is>
+          <t>23:36.237</t>
+        </is>
+      </c>
+      <c r="R1022" t="inlineStr">
+        <is>
+          <t>52161</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1023" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1023" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>SUI</t>
+        </is>
+      </c>
+      <c r="K1023" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1023" t="n">
+        <v>219</v>
+      </c>
+      <c r="M1023" t="n">
+        <v>28</v>
+      </c>
+      <c r="N1023" t="n">
+        <v>28</v>
+      </c>
+      <c r="P1023" t="inlineStr">
+        <is>
+          <t>23:47.385</t>
+        </is>
+      </c>
+      <c r="R1023" t="inlineStr">
+        <is>
+          <t>42378</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1024" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1024" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="K1024" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1024" t="n">
+        <v>218</v>
+      </c>
+      <c r="M1024" t="n">
+        <v>29</v>
+      </c>
+      <c r="N1024" t="n">
+        <v>29</v>
+      </c>
+      <c r="P1024" t="inlineStr">
+        <is>
+          <t>24:32.609</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1025" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1025" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="K1025" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1025" t="n">
+        <v>21</v>
+      </c>
+      <c r="R1025" t="inlineStr">
+        <is>
+          <t>51858</t>
+        </is>
+      </c>
+      <c r="X1025" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1026" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1026" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1026" t="n">
+        <v>21</v>
+      </c>
+      <c r="X1026" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D1027" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1027" s="2" t="n">
+        <v>41763</v>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L1027" t="n">
+        <v>21</v>
+      </c>
+      <c r="X1027" t="inlineStr">
+        <is>
+          <t>DNF</t>
         </is>
       </c>
     </row>
@@ -72994,17 +75305,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Henriette Engel</t>
+          <t>Bridgitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HANSEN</t>
+          <t>HARTLEY</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -73016,17 +75327,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bridgitte</t>
+          <t>Teneale</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HARTLEY</t>
+          <t>HATTON</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -73038,17 +75349,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>42381</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Teneale</t>
+          <t>Livia</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HATTON</t>
+          <t>HAUDENSCHILD</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -73060,17 +75371,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>42381</t>
+          <t>35788</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Livia</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HAUDENSCHILD</t>
+          <t>HAVLOVA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -73082,39 +75393,39 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>35788</t>
+          <t>51867</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Strand</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HAVLOVA</t>
+          <t>HENRIK</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>51867</t>
+          <t>45219</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Strand</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HENRIK</t>
+          <t>HERICS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -73126,17 +75437,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>45219</t>
+          <t>36048</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HERICS</t>
+          <t>HERNANZ AGUERIA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -73148,17 +75459,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HERNANZ AGUERIA</t>
+          <t>HOFF</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -73170,17 +75481,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>42175</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Ervin</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HOFF</t>
+          <t>HOLPERT</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -73192,17 +75503,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>42175</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ervin</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HOLPERT</t>
+          <t>HOLTZ</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -73214,105 +75525,105 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>52174</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Jieyi</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HOLTZ</t>
+          <t>HUANG</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>52174</t>
+          <t>45211</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Jieyi</t>
+          <t>Tibor</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HUANG</t>
+          <t>HUFNAGEL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>45211</t>
+          <t>42260</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tibor</t>
+          <t>Belen</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HUFNAGEL</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>42260</t>
+          <t>45216</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Belen</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>ILYES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>45216</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ILYES</t>
+          <t>INCOLLINGO</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -73324,61 +75635,61 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>36565</t>
+          <t>51914</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Maja Rosenkrans</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>INCOLLINGO</t>
+          <t>IRGENS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>51914</t>
+          <t>52231</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Maja Rosenkrans</t>
+          <t>Ernest</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>IRGENS</t>
+          <t>IRNAZAROV</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>52231</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ernest</t>
+          <t>Gabor</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IRNAZAROV</t>
+          <t>JAKUBIK</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -73390,17 +75701,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>44425</t>
+          <t>44435</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Gabor</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>JAKUBIK</t>
+          <t>JANKOVEC</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -73412,17 +75723,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>44435</t>
+          <t>45123</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>JANKOVEC</t>
+          <t>JANZA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -73434,17 +75745,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>45123</t>
+          <t>42441</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>JANZA</t>
+          <t>JEZIERSKI</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -73456,17 +75767,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>42441</t>
+          <t>52102</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Elenius</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>JEZIERSKI</t>
+          <t>JOEL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -73478,17 +75789,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>52102</t>
+          <t>52103</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Elenius</t>
+          <t>Lilja</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>JOEL</t>
+          <t>JOHAN</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -73500,149 +75811,149 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>52103</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Lilja</t>
+          <t>Karin</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>JOHAN</t>
+          <t>JOHANSSON</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Karin</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>JOHANSSON</t>
+          <t>KACZOR</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>52237</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Kseniya</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KACZOR</t>
+          <t>KALININA</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>42270</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kseniya</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>KALININA</t>
+          <t>KAMINSKI</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>47437</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KAMINSKI</t>
+          <t>KARASZ</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>47437</t>
+          <t>45127</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Kristof</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KARASZ</t>
+          <t>KHAUT</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>45127</t>
+          <t>52230</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Kristof</t>
+          <t>Mirziyodjon</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>KHAUT</t>
+          <t>KHOJIEV</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -73654,17 +75965,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>35713</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mirziyodjon</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>KHOJIEV</t>
+          <t>KIRAJ</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -73676,61 +75987,61 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Ivana</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>KIRAJ</t>
+          <t>KMETOVA</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>44421</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ivana</t>
+          <t>Gerasim</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>KMETOVA</t>
+          <t>KOCHNEV</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>47675</t>
+          <t>47717</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Gerasim</t>
+          <t>Rastislav</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>KOCHNEV</t>
+          <t>KOHUT</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -73742,61 +76053,61 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>47717</t>
+          <t>35779</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Rastislav</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>KOHUT</t>
+          <t>KOZISKOVA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>35779</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>KOZISKOVA</t>
+          <t>KRAJCOVIC</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>45732</t>
+          <t>35872</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Michal</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>KRAJCOVIC</t>
+          <t>KUDLA</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -73808,17 +76119,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>35872</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Michal</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KUDLA</t>
+          <t>KUJAWSKI</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -73830,17 +76141,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KUJAWSKI</t>
+          <t>KULETA</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -73852,17 +76163,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>42032</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Oleksiy</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>KULETA</t>
+          <t>KUPIN</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -73874,17 +76185,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>42032</t>
+          <t>42585</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Oleksiy</t>
+          <t>Ka Wai</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KUPIN</t>
+          <t>KWOK</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -73896,17 +76207,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>42585</t>
+          <t>41993</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ka Wai</t>
+          <t>Aurimas</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>KWOK</t>
+          <t>LANKAS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -73918,17 +76229,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>41993</t>
+          <t>45221</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Aurimas</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LANKAS</t>
+          <t>LANTOS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -73940,61 +76251,61 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>45221</t>
+          <t>46232</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Irina</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LANTOS</t>
+          <t>LAURIC</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>46232</t>
+          <t>41777</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Irina</t>
+          <t>Antti</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LAURIC</t>
+          <t>LAURIKAINEN</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>41777</t>
+          <t>42257</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Antti</t>
+          <t>Andres</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LAURIKAINEN</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -74006,39 +76317,39 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>52497</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Andres</t>
+          <t>Geraldine</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>LEE WEI LING</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Geraldine</t>
+          <t>Ana Roxana</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>LEE WEI LING</t>
+          <t>LEHACI</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -74050,17 +76361,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>52199</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ana Roxana</t>
+          <t>Dongyin</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>LEHACI</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -74072,12 +76383,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>52199</t>
+          <t>52169</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Dongyin</t>
+          <t>Zhangli</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -74094,39 +76405,39 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>52169</t>
+          <t>35720</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Zhangli</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LIEBSCHER</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>35720</t>
+          <t>52099</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Joakim</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>LIEBSCHER</t>
+          <t>LINDBERG</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -74138,127 +76449,127 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>52099</t>
+          <t>52167</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Joakim</t>
+          <t>Haiping</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>LINDBERG</t>
+          <t>LIU</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>52167</t>
+          <t>52148</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Haiping</t>
+          <t>Diogo</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LIU</t>
+          <t>LOPES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>52148</t>
+          <t>51823</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Diogo</t>
+          <t>Jaimee</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>LOPES</t>
+          <t>LOVETT</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>51823</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Jaimee</t>
+          <t>Michal Marek</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LOVETT</t>
+          <t>LUBNIEWSKI</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>35969</t>
+          <t>45226</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Michal Marek</t>
+          <t>Dora</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>LUBNIEWSKI</t>
+          <t>LUCZ</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>45226</t>
+          <t>52173</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dora</t>
+          <t>Qing</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>LUCZ</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -74270,17 +76581,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>52173</t>
+          <t>46674</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Qing</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MACHOVA</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -74292,39 +76603,39 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>46674</t>
+          <t>52206</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Federico</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MACHOVA</t>
+          <t>MANCARELLA</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>52206</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Federico</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MANCARELLA</t>
+          <t>MARON</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -74336,17 +76647,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>52161</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MARON</t>
+          <t>MARQUES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -74358,39 +76669,39 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>52161</t>
+          <t>37571</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MARQUES</t>
+          <t>MATHYS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>37571</t>
+          <t>35897</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Lucie</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MATHYS</t>
+          <t>MATOUSKOVA</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -74402,39 +76713,39 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>52204</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Lucie</t>
+          <t>Fabrizio</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MATOUSKOVA</t>
+          <t>MATTIA</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>52204</t>
+          <t>45118</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Fabrizio</t>
+          <t>Taras</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MATTIA</t>
+          <t>MATVIICHUK</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -74446,61 +76757,61 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>45118</t>
+          <t>52179</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Taras</t>
+          <t>Catherine</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MATVIICHUK</t>
+          <t>MCARTHUR</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>51826</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Catherine</t>
+          <t>Marty</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MCARTHUR</t>
+          <t>MCDOWELL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>51826</t>
+          <t>52177</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Marty</t>
+          <t>Merey</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MCDOWELL</t>
+          <t>MEDETOV</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -74512,17 +76823,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>52177</t>
+          <t>51786</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Merey</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MEDETOV</t>
+          <t>MEUNIER</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -74534,17 +76845,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>51786</t>
+          <t>44426</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Matej</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MEUNIER</t>
+          <t>MICHALEK</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -74556,17 +76867,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>44426</t>
+          <t>47252</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Matej</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>MICHALEK</t>
+          <t>MIHALACHI</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -74578,17 +76889,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>47252</t>
+          <t>51915</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Jonas</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MIHALACHI</t>
+          <t>MIKAEL EL ASWY</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -74600,17 +76911,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>51915</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Jonas</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>MIKAEL EL ASWY</t>
+          <t>MIKE</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -74622,17 +76933,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>47427</t>
+          <t>52229</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Serik</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MIKE</t>
+          <t>MIRBEKOV</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -74644,17 +76955,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>35556</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Serik</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>MIRBEKOV</t>
+          <t>MISKOVSKY</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -74666,17 +76977,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>35556</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Radek</t>
+          <t>Aleksey</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>MISKOVSKY</t>
+          <t>MOCHALOV</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -74688,17 +76999,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>42305</t>
+          <t>51858</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Uros</t>
+          <t>Yuen Fung</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>MITJEV</t>
+          <t>MOK</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -74710,39 +77021,39 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>52228</t>
+          <t>42187</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Aleksey</t>
+          <t>Nikolina</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MOCHALOV</t>
+          <t>MOLDOVAN</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>51858</t>
+          <t>47423</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Yuen Fung</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MOK</t>
+          <t>MOLNAR</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -74754,39 +77065,39 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>42187</t>
+          <t>42389</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Nikolina</t>
+          <t>Ruslan</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MOLDOVAN</t>
+          <t>MOLTAEV</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>47423</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>MOLNAR</t>
+          <t>MORNEAU</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -74798,39 +77109,39 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>42389</t>
+          <t>36562</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ruslan</t>
+          <t>Norma</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>MOLTAEV</t>
+          <t>MURABITO</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>42464</t>
+          <t>36731</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Tamerlan</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>MORNEAU</t>
+          <t>MUSTAFAYEV</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -74842,17 +77153,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>52281</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Norma</t>
+          <t>Flora</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>MURABITO</t>
+          <t>NAGY</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -74864,17 +77175,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>36731</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Tamerlan</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MUSTAFAYEV</t>
+          <t>NAGY</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -74886,17 +77197,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Flora</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>NAGY</t>
+          <t>NAJA</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -74908,17 +77219,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>47634</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NAGY</t>
+          <t>NATHELL</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -74930,17 +77241,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>35557</t>
+          <t>53045</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Annabelle</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>NAJA</t>
+          <t>NG XIANG RU</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -74952,83 +77263,83 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>42427</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Federica</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>NATHELL</t>
+          <t>NOLE</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>53045</t>
+          <t>42181</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Annabelle</t>
+          <t>Marko</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>NG XIANG RU</t>
+          <t>NOVAKOVIC</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Federica</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>NOLE</t>
+          <t>OLDERSHAW</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>36635</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Marko</t>
+          <t>Ronilson Matias</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>NOVAKOVIC</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -75040,17 +77351,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>38164</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>OLDERSHAW</t>
+          <t>OVEN</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -75062,17 +77373,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>36635</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ronilson Matias</t>
+          <t>Dejan</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>PAJIC</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -75084,39 +77395,39 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>38164</t>
+          <t>51871</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>OVEN</t>
+          <t>PALDANIUS</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Dejan</t>
+          <t>Aleksandr</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>PAJIC</t>
+          <t>PAROL</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -75128,83 +77439,83 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>46830</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Inigo</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>PALDANIUS</t>
+          <t>PENA</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>51940</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Aleksandr</t>
+          <t>Stefanie</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>PAROL</t>
+          <t>PERDOMO</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>46830</t>
+          <t>52295</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Inigo</t>
+          <t>Mayara Cardoso A</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>PENA</t>
+          <t>PEREIRA</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>51940</t>
+          <t>42842</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Stefanie</t>
+          <t>Emilie Ahmt</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>PERDOMO</t>
+          <t>PETERSEN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -75216,17 +77527,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>52295</t>
+          <t>42426</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Mayara Cardoso A</t>
+          <t>Cristina</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>PEREIRA</t>
+          <t>PETRACCA</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -75238,83 +77549,83 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>42842</t>
+          <t>42569</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Emilie Ahmt</t>
+          <t>Vladimir</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>PETERSEN</t>
+          <t>PETROV</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>42426</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Cristina</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>PETRACCA</t>
+          <t>PIMENTA</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>42569</t>
+          <t>52294</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Vladimir</t>
+          <t>Ariela Cesar</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>PETROV</t>
+          <t>PINTO</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>36436</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PIMENTA</t>
+          <t>PISTRITTO</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -75326,17 +77637,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>52294</t>
+          <t>47296</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Ariela Cesar</t>
+          <t>Veronica Yoko</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PINTO</t>
+          <t>PLEBANI</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -75348,17 +77659,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>36436</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Rene Holten</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>PISTRITTO</t>
+          <t>POULSEN</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -75370,39 +77681,39 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>47296</t>
+          <t>35863</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Veronica Yoko</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>PLEBANI</t>
+          <t>PUTTO</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>35549</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Rene Holten</t>
+          <t>Jaroslav</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>POULSEN</t>
+          <t>RADON</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -75414,17 +77725,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>35863</t>
+          <t>41994</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Edvinas</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>PUTTO</t>
+          <t>RAMANAUSKAS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -75436,17 +77747,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>35549</t>
+          <t>35724</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Jaroslav</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>RADON</t>
+          <t>RAUHE</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -75458,17 +77769,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>41994</t>
+          <t>47299</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Edvinas</t>
+          <t>Salvatore</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>RAMANAUSKAS</t>
+          <t>RAVALLI</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -75480,17 +77791,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>35724</t>
+          <t>46847</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>RAUHE</t>
+          <t>REJA</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -75502,39 +77813,39 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>47299</t>
+          <t>52168</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Salvatore</t>
+          <t>Wenjun</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>RAVALLI</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>46847</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>REJA</t>
+          <t>RICCHETTI</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -75546,39 +77857,39 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>52168</t>
+          <t>36568</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Wenjun</t>
+          <t>Nicola</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>RIPAMONTI</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>36566</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>Manfredi</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>RICCHETTI</t>
+          <t>RIZZA</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -75590,105 +77901,105 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>36568</t>
+          <t>52180</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Nicola</t>
+          <t>Jaime</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>RIPAMONTI</t>
+          <t>ROBERTS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>45520</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Manfredi</t>
+          <t>Bren</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>RIZZA</t>
+          <t>RODRIGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>52180</t>
+          <t>35862</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Jaime</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ROBERTS</t>
+          <t>ROSOLSKI</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>45520</t>
+          <t>51907</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Bren</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>RODRIGUEZ GUTIERREZ</t>
+          <t>ROY</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>35862</t>
+          <t>44427</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Matej</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ROSOLSKI</t>
+          <t>RUSNAK</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -75700,17 +78011,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>51907</t>
+          <t>46671</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Vojtech</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ROY</t>
+          <t>RUSO</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -75722,17 +78033,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>44427</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Matej</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>RUSNAK</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -75744,39 +78055,39 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>46671</t>
+          <t>42189</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Vojtech</t>
+          <t>Dalma</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>RUSO</t>
+          <t>RUZICIC-BENEDEK</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>41779</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Mykyta</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>SABLIN</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -75788,83 +78099,83 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>42189</t>
+          <t>36563</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Dalma</t>
+          <t>Daniele</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>RUZICIC-BENEDEK</t>
+          <t>SANTINI</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>41779</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Mykyta</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>SABLIN</t>
+          <t>SCHURING</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Daniele</t>
+          <t>Viktoria</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>SANTINI</t>
+          <t>SCHWARZ</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>52506</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Yvonne</t>
+          <t>Suzanne</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>SCHURING</t>
+          <t>SEAH</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -75876,39 +78187,39 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>41776</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Viktoria</t>
+          <t>Eero</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>SCHWARZ</t>
+          <t>SELIVAARA</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>52506</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Suzanne</t>
+          <t>Natalya</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>SEAH</t>
+          <t>SERGEYEVA</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -75920,17 +78231,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>41776</t>
+          <t>52205</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Eero</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SELIVAARA</t>
+          <t>SGARAVATTO</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -75942,39 +78253,39 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>42573</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Natalya</t>
+          <t>Mario</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>SERGEYEVA</t>
+          <t>SIEGL</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>52205</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>SGARAVATTO</t>
+          <t>SIEMIONOWSKI</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -75986,17 +78297,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Mario</t>
+          <t>Emanuel</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>SIEGL</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -76008,17 +78319,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>35858</t>
+          <t>36634</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Erlon De Souza</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>SIEMIONOWSKI</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -76030,17 +78341,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>36449</t>
+          <t>35869</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Emanuel</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>SLOMINSKI</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -76052,17 +78363,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>36634</t>
+          <t>52015</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Erlon De Souza</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>SONDERBY THOMSEN</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -76074,17 +78385,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>35869</t>
+          <t>42596</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>Bartosz</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>SLOMINSKI</t>
+          <t>STABNO</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -76096,105 +78407,105 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>52015</t>
+          <t>46062</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Staniliya</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>SONDERBY THOMSEN</t>
+          <t>STAMENOVA</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>42596</t>
+          <t>47622</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>STABNO</t>
+          <t>STENSILS</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>46062</t>
+          <t>45793</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Staniliya</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>STAMENOVA</t>
+          <t>STEWART</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>47622</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>STENSILS</t>
+          <t>SVAB</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>47627</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>STEWART</t>
+          <t>SVANQVIST</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -76206,39 +78517,39 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>42378</t>
+          <t>41542</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Andri</t>
+          <t>Gabriella</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>SUMMERMATTER</t>
+          <t>SZABO</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>SVAB</t>
+          <t>SZANDRACH</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -76250,17 +78561,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>47627</t>
+          <t>35931</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>SVANQVIST</t>
+          <t>SZYPULA</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -76272,61 +78583,61 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>41542</t>
+          <t>42171</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Gabriella</t>
+          <t>Lachlan</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>SZABO</t>
+          <t>TAME</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Amalie Ringtved</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>SZANDRACH</t>
+          <t>THOMSEN</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>35931</t>
+          <t>52225</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Artur</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>SZYPULA</t>
+          <t>TOM</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -76338,17 +78649,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>42171</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Lachlan</t>
+          <t>Marko</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>TAME</t>
+          <t>TOMICEVIC</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -76360,39 +78671,39 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>42349</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Amalie Ringtved</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>THOMSEN</t>
+          <t>TORNEO</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>52225</t>
+          <t>46841</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Cristian</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>TOM</t>
+          <t>TORO</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -76404,17 +78715,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>42184</t>
+          <t>42185</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Marko</t>
+          <t>Vladimir</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>TOMICEVIC</t>
+          <t>TORUBAROV</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -76426,17 +78737,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>42420</t>
+          <t>45218</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Sandor</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>TORNEO</t>
+          <t>TOTKA</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -76448,17 +78759,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>46841</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Cristian</t>
+          <t>Aleksandr</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>TORO</t>
+          <t>TROPIN</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -76470,127 +78781,127 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>42185</t>
+          <t>52239</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Vladimir</t>
+          <t>Yuliya</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>TORUBAROV</t>
+          <t>TSOY</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>45218</t>
+          <t>52235</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Sandor</t>
+          <t>Olga</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>TOTKA</t>
+          <t>UMARALIEVA</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>47435</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Aleksandr</t>
+          <t>Ninetta</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>TROPIN</t>
+          <t>VAD</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>52239</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Yuliya</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>TSOY</t>
+          <t>VAN KOEVERDEN</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>52235</t>
+          <t>47426</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Olga</t>
+          <t>Henrik</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>UMARALIEVA</t>
+          <t>VASBANYAI</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>47435</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Ninetta</t>
+          <t>Oona</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>VAD</t>
+          <t>VASKO</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -76602,39 +78913,39 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>42770</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Ana Paula</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>VAN KOEVERDEN</t>
+          <t>VERGUTZ</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>47426</t>
+          <t>45222</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Henrik</t>
+          <t>Viktor</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>VASBANYAI</t>
+          <t>VIOLA</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -76646,17 +78957,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Oona</t>
+          <t>Sabine</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>VASKO</t>
+          <t>VOLZ</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -76668,17 +78979,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>42770</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Ana Paula</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>VERGUTZ</t>
+          <t>WALCZYKIEWICZ</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -76690,17 +79001,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>42346</t>
+          <t>42209</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Ida</t>
+          <t>Bernadette</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>VILLUMSEN</t>
+          <t>WALLACE</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -76712,17 +79023,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>45222</t>
+          <t>42161</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Viktor</t>
+          <t>Kenny</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>VIOLA</t>
+          <t>WALLACE</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -76734,17 +79045,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Sabine</t>
+          <t>Conny</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>VOLZ</t>
+          <t>WASSMUTH</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -76756,39 +79067,39 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>WALCZYKIEWICZ</t>
+          <t>WATKINS</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>42209</t>
+          <t>47624</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Bernadette</t>
+          <t>Moa</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>WALLACE</t>
+          <t>WIKBERG</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -76800,39 +79111,39 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>51620</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Kenny</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>WALLACE</t>
+          <t>WLOSIK</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Conny</t>
+          <t>Ewelina</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>WASSMUTH</t>
+          <t>WOJNAROWSKA</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -76844,17 +79155,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>47415</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>WATKINS</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -76866,17 +79177,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>47624</t>
+          <t>52171</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Moa</t>
+          <t>Yanan</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>WIKBERG</t>
+          <t>WU</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -76888,39 +79199,39 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>51620</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>WLOSIK</t>
+          <t>WYSS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>52198</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Caihong</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>WOJNAROWSKA</t>
+          <t>XU</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -76932,17 +79243,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>47415</t>
+          <t>46593</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Cagribey</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>YILDIRIM</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -76954,39 +79265,39 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>52171</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Yanan</t>
+          <t>Jost</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>WU</t>
+          <t>ZAKRAJSEK</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>44432</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Miroslav</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>WYSS</t>
+          <t>ZATKO</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -76998,17 +79309,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>52198</t>
+          <t>52182</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Caihong</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>XU</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -77020,17 +79331,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>46593</t>
+          <t>42179</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Cagribey</t>
+          <t>Milenko</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>YILDIRIM</t>
+          <t>ZORIC</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -77042,110 +79353,110 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>42444</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Jost</t>
+          <t>Anja</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>ZAKRAJSEK</t>
+          <t>OSTERMAN</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>44432</t>
+          <t>42337</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Miroslav</t>
+          <t>Henriette Engel</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ZATKO</t>
+          <t>HANSEN</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>52182</t>
+          <t>42378</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Andri</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>ZHOU</t>
+          <t>SUMMERMATTER</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Milenko</t>
+          <t>Ida</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>ZORIC</t>
+          <t>VILLUMSEN</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>42444</t>
+          <t>42305</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Anja</t>
+          <t>Uros</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>OSTERMAN</t>
+          <t>MITJEV</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>

--- a/events/Milan_2014_WC/Milan_2014_WC_Results.xlsx
+++ b/events/Milan_2014_WC/Milan_2014_WC_Results.xlsx
@@ -6576,6 +6576,11 @@
           <t>+32.092</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>52581</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6916,6 +6921,11 @@
           <t>+6.528</t>
         </is>
       </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>36043</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8451,6 +8461,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9236,6 +9251,11 @@
           <t>46671</t>
         </is>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12160,6 +12180,11 @@
           <t>+10.884</t>
         </is>
       </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>49751</t>
+        </is>
+      </c>
       <c r="S167" t="inlineStr">
         <is>
           <t>52099</t>
@@ -12490,6 +12515,11 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
       <c r="T171" t="inlineStr">
         <is>
           <t>52225</t>
@@ -17580,6 +17610,11 @@
           <t>+0.132</t>
         </is>
       </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>36043</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -17995,6 +18030,11 @@
           <t>+23.632</t>
         </is>
       </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>52581</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -19300,6 +19340,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -20010,6 +20055,11 @@
           <t>46671</t>
         </is>
       </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -21060,6 +21110,11 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
       <c r="T294" t="inlineStr">
         <is>
           <t>52225</t>
@@ -21135,6 +21190,11 @@
           <t>+0.980</t>
         </is>
       </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>49751</t>
+        </is>
+      </c>
       <c r="S295" t="inlineStr">
         <is>
           <t>52099</t>
@@ -21705,6 +21765,11 @@
           <t>+8.660</t>
         </is>
       </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>41773</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -23000,6 +23065,11 @@
           <t>+11.000</t>
         </is>
       </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>52581</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -25105,6 +25175,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -25245,6 +25320,11 @@
           <t>44434</t>
         </is>
       </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>44441</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -25685,6 +25765,11 @@
           <t>51867</t>
         </is>
       </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>49751</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -26645,6 +26730,11 @@
           <t>46671</t>
         </is>
       </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -27799,6 +27889,11 @@
           <t>+11.408</t>
         </is>
       </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>41773</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -28694,6 +28789,11 @@
           <t>51867</t>
         </is>
       </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>49751</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -29103,6 +29203,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
       <c r="X409" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -30068,6 +30173,11 @@
           <t>46671</t>
         </is>
       </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -32517,6 +32627,11 @@
           <t>+3.436</t>
         </is>
       </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>36043</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -33885,6 +34000,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -36736,6 +36856,11 @@
           <t>+11.024</t>
         </is>
       </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>49751</t>
+        </is>
+      </c>
       <c r="S513" t="inlineStr">
         <is>
           <t>52099</t>
@@ -36823,6 +36948,11 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
       <c r="T514" t="inlineStr">
         <is>
           <t>52225</t>
@@ -42134,6 +42264,11 @@
           <t>+3.536</t>
         </is>
       </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>41773</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -43089,6 +43224,11 @@
           <t>+3.976</t>
         </is>
       </c>
+      <c r="R601" t="inlineStr">
+        <is>
+          <t>52581</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -51898,6 +52038,11 @@
           <t>+2.856</t>
         </is>
       </c>
+      <c r="R726" t="inlineStr">
+        <is>
+          <t>41773</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -51963,6 +52108,11 @@
           <t>+5.144</t>
         </is>
       </c>
+      <c r="R727" t="inlineStr">
+        <is>
+          <t>52581</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -65875,6 +66025,11 @@
           <t>+2.652</t>
         </is>
       </c>
+      <c r="R921" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -67238,6 +67393,11 @@
           <t>+9.208</t>
         </is>
       </c>
+      <c r="R940" t="inlineStr">
+        <is>
+          <t>41773</t>
+        </is>
+      </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
@@ -67613,6 +67773,11 @@
           <t>44434</t>
         </is>
       </c>
+      <c r="S945" t="inlineStr">
+        <is>
+          <t>44441</t>
+        </is>
+      </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
@@ -67911,6 +68076,11 @@
           <t>51867</t>
         </is>
       </c>
+      <c r="S949" t="inlineStr">
+        <is>
+          <t>49751</t>
+        </is>
+      </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
@@ -68738,6 +68908,11 @@
           <t>42260</t>
         </is>
       </c>
+      <c r="S960" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
@@ -72217,6 +72392,11 @@
           <t>22:36.113</t>
         </is>
       </c>
+      <c r="R1011" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
@@ -72676,6 +72856,11 @@
           <t>23:17.069</t>
         </is>
       </c>
+      <c r="R1018" t="inlineStr">
+        <is>
+          <t>49751</t>
+        </is>
+      </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
@@ -73071,6 +73256,11 @@
       <c r="P1024" t="inlineStr">
         <is>
           <t>24:32.609</t>
+        </is>
+      </c>
+      <c r="R1024" t="inlineStr">
+        <is>
+          <t>52581</t>
         </is>
       </c>
     </row>
@@ -73258,7 +73448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D282"/>
+  <dimension ref="A1:D291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79460,6 +79650,204 @@
         </is>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>DRAHOKOUPIL</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>36043</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>CUBELOS</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Miika</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>NYKAENEN</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>41773</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Janne</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>MAENTYNEN</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>44441</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Juraj</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>TARR</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>49751</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Emil</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>SVENSSON</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>52581</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Brandon Wei Cheng</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>OOI</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Vyacheslav</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>GORN</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Mia</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>FRIEND CHUNG</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Milan_2014_WC/Milan_2014_WC_Results.xlsx
+++ b/events/Milan_2014_WC/Milan_2014_WC_Results.xlsx
@@ -43984,6 +43984,11 @@
           <t>40.316</t>
         </is>
       </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -62944,6 +62949,11 @@
       <c r="Q879" t="inlineStr">
         <is>
           <t>+0.964</t>
+        </is>
+      </c>
+      <c r="R879" t="inlineStr">
+        <is>
+          <t>36633</t>
         </is>
       </c>
     </row>
@@ -73448,7 +73458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D291"/>
+  <dimension ref="A1:D292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79848,6 +79858,28 @@
         </is>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Nivalter</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Santos JESUS</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
